--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123191898</v>
+        <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellansjön, Vislanda, Sm</t>
+          <t>Obyskogen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468925</v>
+        <v>468792</v>
       </c>
       <c r="R2" t="n">
-        <v>6294850</v>
+        <v>6294894</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,30 +770,41 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123191898</t>
+          <t>https://artportalen.se/Sighting/137013827</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123770277</v>
+        <v>123191898</v>
       </c>
       <c r="B3" t="n">
         <v>57950</v>
@@ -816,27 +833,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallåsen, Sm</t>
+          <t>Mellansjön, Vislanda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468744</v>
+        <v>468925</v>
       </c>
       <c r="R3" t="n">
-        <v>6294838</v>
+        <v>6294850</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,16 +894,126 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123191898</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123770277</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tallåsen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468744</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6294838</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blädinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123770277</t>
         </is>
@@ -899,6 +1023,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1811-2025 artfynd.xlsx
+++ b/artfynd/A 1811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137013827</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
